--- a/taxonomy/taxonomy.xlsx
+++ b/taxonomy/taxonomy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dltkd\Desktop\261004 BEOL AX day2\taxonomy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8B735D-FE18-4D9C-B6BA-57795C95A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14790CF2-3FA2-4550-926A-7F2AEBFD15BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="17280" xr2:uid="{4839889B-8E27-4F13-89D4-7E9141DB71F6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="338">
   <si>
     <t>축</t>
   </si>
@@ -197,12 +197,6 @@
     <t>Materials</t>
   </si>
   <si>
-    <t>소재 변경</t>
-  </si>
-  <si>
-    <t>slurry B</t>
-  </si>
-  <si>
     <t>Scheme</t>
   </si>
   <si>
@@ -356,9 +350,6 @@
     <t>Void</t>
   </si>
   <si>
-    <t>충진 내부 공극, seam</t>
-  </si>
-  <si>
     <t>보이드</t>
   </si>
   <si>
@@ -870,14 +861,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>각 layer별 Main 공정에 대한 step terminology</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AASI, AMI, ACI, ASI, AEI, ASEI, API</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>X3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -939,49 +922,209 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Line 저항 상승, CMBSRP 저항 상승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ru</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruthenium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thickness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AASI</t>
+  </si>
+  <si>
+    <t>ASEI</t>
+  </si>
+  <si>
+    <t>AMI</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>AEI</t>
+  </si>
+  <si>
+    <t>ASI</t>
+  </si>
+  <si>
+    <t>I1은 M1 layer에서 SAUP 혹은 r-SAUP공정을 적용할 때 진행되는 photo layer의 이름</t>
+  </si>
+  <si>
+    <t>평가에서 소재의 종류나 조성 자체를 변경하는 범주</t>
+  </si>
+  <si>
+    <t>소재 종류·조성 변경</t>
+  </si>
+  <si>
+    <t>소재명이 언급될 뿐 변경 변수는 레시피나 증착 방식인 경우</t>
+  </si>
+  <si>
+    <t>MHC</t>
+  </si>
+  <si>
     <t>Via 저항 상승, Via Rc 상승</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line 저항 상승, CMBSRP 저항 상승</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ru</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruthenium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단면에서 관찰된 충진 내부 공극 또는 seam</t>
+  </si>
+  <si>
+    <t>배선 또는 비아 내부의 void·seam 관찰</t>
+  </si>
+  <si>
+    <t>공극 관찰 없이 전기적 특성만으로 추정한 경우</t>
+  </si>
+  <si>
+    <t>bottom low-k PID(C-H 결합 손실)</t>
+  </si>
+  <si>
+    <t>Cu Dual damascene</t>
+  </si>
+  <si>
+    <t>Cu dual damascene</t>
+  </si>
+  <si>
+    <t>Cu/TaN residue bridge</t>
+  </si>
+  <si>
+    <t>HDLK</t>
+  </si>
+  <si>
+    <t>I1 Line</t>
+  </si>
+  <si>
+    <t>I1 배선층</t>
+  </si>
+  <si>
+    <t>line 간 bridge short</t>
+  </si>
+  <si>
+    <t>low-k plasma damaged layer</t>
+  </si>
+  <si>
+    <t>Ru TopVia / airgap</t>
+  </si>
+  <si>
+    <t>Ru line bottom bridge</t>
+  </si>
+  <si>
+    <t>Short fail die</t>
+  </si>
+  <si>
+    <t>Short 불량</t>
+  </si>
+  <si>
+    <t>SiN HM 유도 산화/소실</t>
+  </si>
+  <si>
+    <t>SiN HM</t>
+  </si>
+  <si>
+    <t>SiN 하드마스크 층</t>
+  </si>
+  <si>
+    <t>TiN</t>
+  </si>
+  <si>
+    <t>VCHN Short</t>
+  </si>
+  <si>
+    <t>VCHN 쇼트 불량</t>
+  </si>
+  <si>
+    <t>via bottom void</t>
+  </si>
+  <si>
+    <t>비아 바닥 보이드</t>
+  </si>
+  <si>
+    <t>seam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유의차 없음</t>
+  </si>
+  <si>
+    <t>두께</t>
   </si>
   <si>
     <t>THK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thickness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AASI</t>
-  </si>
-  <si>
-    <t>ASEI</t>
-  </si>
-  <si>
-    <t>AMI</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>AEI</t>
-  </si>
-  <si>
-    <t>ASI</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>V0 표기를 구조/레이어 VA로 정규화한다.</t>
+  </si>
+  <si>
+    <t>Airgap+cap opt</t>
+  </si>
+  <si>
+    <t>CMP 미연마</t>
+  </si>
+  <si>
+    <t>low-k PID</t>
+  </si>
+  <si>
+    <t>Ru direct metal etch</t>
+  </si>
+  <si>
+    <t>Ru subtractive</t>
+  </si>
+  <si>
+    <t>Open fail die</t>
+  </si>
+  <si>
+    <t>Open 불량</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I2은 M2 layer에서 SAUP 혹은 r-SAUP공정을 적용할 때 진행되는 photo layer의 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 자료의 SEM, TEM 단면이미지를 확인한 step이나, 평가 목적에 해당하는 step을 main step이라고 한다.</t>
+  </si>
+  <si>
+    <t>평가 목적에 해당 step명이 명시된 경우에는 포함한다.</t>
+  </si>
+  <si>
+    <t>Patterning/scheme</t>
+  </si>
+  <si>
+    <t>SAV</t>
+  </si>
+  <si>
+    <t>Cu dual damascene의 AIO (all-in-one) etch시 line hardmask에 의해 via CD가 커지지 않고 self align되는 현상을 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cu dual damascene의 AIO (all-in-one) etch시line trench etch를 먼저 수행하는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trench-first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1388,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F15EC9-954C-4C88-B8BE-47E850B236C8}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1448,7 +1591,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
@@ -1485,7 +1628,7 @@
         <v>18</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -1493,13 +1636,13 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -1507,13 +1650,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>252</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
@@ -1521,13 +1664,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
@@ -1535,10 +1678,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>255</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -1546,7 +1692,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>18</v>
@@ -1557,13 +1703,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>266</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
@@ -1571,13 +1714,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>257</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>205</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -1585,13 +1728,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
@@ -1599,13 +1742,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -1613,10 +1756,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
@@ -1624,10 +1770,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
@@ -1635,13 +1781,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
@@ -1649,10 +1792,13 @@
         <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
@@ -1660,7 +1806,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>22</v>
@@ -1671,13 +1817,10 @@
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
@@ -1685,56 +1828,57 @@
         <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1744,12 +1888,11 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C24" s="3"/>
+        <v>279</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1757,10 +1900,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -1770,10 +1913,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -1783,10 +1926,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1796,10 +1939,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>289</v>
+        <v>251</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1809,10 +1952,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1821,40 +1964,36 @@
       <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>31</v>
+      <c r="D31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
@@ -1862,842 +2001,846 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="H36" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>46</v>
+      <c r="D43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>54</v>
+        <v>286</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+        <v>287</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>63</v>
+        <v>265</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>271</v>
+        <v>64</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>71</v>
+        <v>265</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>191</v>
+        <v>68</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="I60" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>74</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="H62" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="H66" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>14</v>
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="H74" s="1" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>108</v>
+        <v>292</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>196</v>
+        <v>109</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>125</v>
+        <v>99</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D91" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A92" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A92" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
+      <c r="G92" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -2705,7 +2848,7 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
@@ -2713,10 +2856,10 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -2724,7 +2867,7 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2" t="s">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
@@ -2732,88 +2875,149 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>277</v>
+        <v>29</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
+      <c r="H95" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>81</v>
+        <v>272</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="2" t="s">
-        <v>278</v>
-      </c>
+      <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A99" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>83</v>
-      </c>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A98" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A102" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A104" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A105" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -2834,27 +3038,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" t="s">
         <v>145</v>
-      </c>
-      <c r="B1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2868,7 +3072,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BE763F-F860-4673-B5C6-1AFD581A46AB}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.25" bestFit="1" customWidth="1"/>
@@ -2877,483 +3081,769 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C21" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C36" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C41" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B42" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C42" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B43" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B44" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>294</v>
+      </c>
+      <c r="B45" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>295</v>
+      </c>
+      <c r="B46" t="s">
+        <v>296</v>
+      </c>
+      <c r="C46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C49" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>301</v>
+      </c>
+      <c r="B50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>302</v>
+      </c>
+      <c r="B51" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>303</v>
+      </c>
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>304</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>305</v>
+      </c>
+      <c r="B55" t="s">
+        <v>306</v>
+      </c>
+      <c r="C55" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>307</v>
+      </c>
+      <c r="B56" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>310</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>308</v>
+      </c>
+      <c r="B58" t="s">
+        <v>309</v>
+      </c>
+      <c r="C58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>311</v>
+      </c>
+      <c r="B59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B60" t="s">
+        <v>314</v>
+      </c>
+      <c r="C60" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>316</v>
+      </c>
+      <c r="B62" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" t="s">
+        <v>318</v>
+      </c>
+      <c r="C63" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>319</v>
+      </c>
+      <c r="B64" t="s">
+        <v>320</v>
+      </c>
+      <c r="C64" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>322</v>
+      </c>
+      <c r="B65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>323</v>
+      </c>
+      <c r="B66" t="s">
+        <v>109</v>
+      </c>
+      <c r="C66" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B67" t="s">
+        <v>251</v>
+      </c>
+      <c r="C67" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>324</v>
+      </c>
+      <c r="B68" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>325</v>
+      </c>
+      <c r="B69" t="s">
+        <v>326</v>
+      </c>
+      <c r="C69" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>327</v>
+      </c>
+      <c r="B70" t="s">
+        <v>328</v>
+      </c>
+      <c r="C70" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3372,13 +3862,13 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
